--- a/outputs/results_log.xlsx
+++ b/outputs/results_log.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -40,8 +40,18 @@
       <color rgb="00006100"/>
       <sz val="10"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="009C0006"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="0000B050"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -63,6 +73,11 @@
         <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFCCCC"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -76,7 +91,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -89,6 +104,19 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -455,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:L23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -633,8 +661,1160 @@
       <c r="K4" s="3" t="inlineStr"/>
       <c r="L4" s="3" t="inlineStr"/>
     </row>
+    <row r="5" ht="16" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>NSH @ TBL</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>PL</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>NSH +1.5</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>-150</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>+13.7%</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>1.0u</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>+0.67u</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="16" customHeight="1">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>DAL @ PHI</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>PHI ML</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>+140</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>+11.2%</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>1.0u</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>+1.40u</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="16" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>CHI @ NJD</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>PL</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>CHI +1.5</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>-188</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>+9.0%</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>1.0u</t>
+        </is>
+      </c>
+      <c r="J7" s="5" t="inlineStr">
+        <is>
+          <t>-1.00u</t>
+        </is>
+      </c>
+      <c r="K7" s="5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="L7" s="5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="16" customHeight="1">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>BOS @ CBJ</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>PL</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>BOS +1.5</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>-192</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>+8.2%</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>1.0u</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>+0.52u</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="16" customHeight="1">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>NSH @ TBL</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>NSH ML</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>+164</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>+7.9%</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>1.0u</t>
+        </is>
+      </c>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>-1.00u</t>
+        </is>
+      </c>
+      <c r="K9" s="5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L9" s="5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="16" customHeight="1">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>NSH @ TBL</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>OU</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>UNDER 6.5</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>-104</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>+4.5%</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>1.0u</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>+0.96u</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="16" customHeight="1">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>DAL @ PHI</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>OU</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>OVER 5.5</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>-128</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>+4.5%</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>1.0u</t>
+        </is>
+      </c>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>-1.00u</t>
+        </is>
+      </c>
+      <c r="K11" s="5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L11" s="5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="16" customHeight="1">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>BOS @ CBJ</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>BOS ML</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>+130</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>+4.2%</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>1.0u</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>+1.30u</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="16" customHeight="1">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>CHI @ NJD</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>CHI ML</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>+138</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>+4.0%</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>1.0u</t>
+        </is>
+      </c>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>-1.00u</t>
+        </is>
+      </c>
+      <c r="K13" s="5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="L13" s="5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="16" customHeight="1">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>NSH @ TBL</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>PL</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>NSH +1.5</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>-150</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>+13.7%</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>1.0u</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>+0.67u</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="16" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>DAL @ PHI</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>PHI ML</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>+140</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>+11.2%</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>1.0u</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>+1.40u</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="16" customHeight="1">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>CHI @ NJD</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>PL</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>CHI +1.5</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>-188</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>+9.0%</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>1.0u</t>
+        </is>
+      </c>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>-1.00u</t>
+        </is>
+      </c>
+      <c r="K16" s="5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="L16" s="5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="16" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>BOS @ CBJ</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>PL</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>BOS +1.5</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>-192</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>+8.2%</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>1.0u</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>+0.52u</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="16" customHeight="1">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>NSH @ TBL</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>NSH ML</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>+164</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>+7.9%</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="H18" s="5" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t>1.0u</t>
+        </is>
+      </c>
+      <c r="J18" s="5" t="inlineStr">
+        <is>
+          <t>-1.00u</t>
+        </is>
+      </c>
+      <c r="K18" s="5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L18" s="5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="16" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>NSH @ TBL</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>OU</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>UNDER 6.5</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>-104</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>+4.5%</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>1.0u</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>+0.96u</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="16" customHeight="1">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>DAL @ PHI</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>OU</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>OVER 5.5</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>-128</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>+4.5%</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="H20" s="5" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="I20" s="5" t="inlineStr">
+        <is>
+          <t>1.0u</t>
+        </is>
+      </c>
+      <c r="J20" s="5" t="inlineStr">
+        <is>
+          <t>-1.00u</t>
+        </is>
+      </c>
+      <c r="K20" s="5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L20" s="5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="16" customHeight="1">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>BOS @ CBJ</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>BOS ML</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>+130</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>+4.2%</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>1.0u</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>+1.30u</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="16" customHeight="1">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>CHI @ NJD</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>CHI ML</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>+138</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>+4.0%</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="H22" s="5" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="I22" s="5" t="inlineStr">
+        <is>
+          <t>1.0u</t>
+        </is>
+      </c>
+      <c r="J22" s="5" t="inlineStr">
+        <is>
+          <t>-1.00u</t>
+        </is>
+      </c>
+      <c r="K22" s="5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="L22" s="5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="18" customHeight="1">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>SEASON TOTALS</t>
+        </is>
+      </c>
+      <c r="E23" s="8" t="inlineStr"/>
+      <c r="F23" s="8" t="inlineStr"/>
+      <c r="G23" s="8" t="inlineStr"/>
+      <c r="H23" s="7" t="inlineStr">
+        <is>
+          <t>12W / 8L / 0P</t>
+        </is>
+      </c>
+      <c r="I23" s="7" t="inlineStr">
+        <is>
+          <t>20u</t>
+        </is>
+      </c>
+      <c r="J23" s="9" t="inlineStr">
+        <is>
+          <t>+3.69u</t>
+        </is>
+      </c>
+      <c r="K23" s="7" t="inlineStr">
+        <is>
+          <t>W%: 60.0%</t>
+        </is>
+      </c>
+      <c r="L23" s="9" t="inlineStr">
+        <is>
+          <t>ROI: +18.4%</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
+    <mergeCell ref="A23:D23"/>
     <mergeCell ref="A1:L1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
